--- a/output/stock_quant_scores/INTC_balance_df.xlsx
+++ b/output/stock_quant_scores/INTC_balance_df.xlsx
@@ -1711,23 +1711,33 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>38110000000</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>31096000000</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>95391000000</v>
+      </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>68265000000</v>
+      </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>73015000000</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
@@ -1747,7 +1757,9 @@
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>27462000000</v>
+      </c>
       <c r="AG6" t="n">
         <v>2000000000</v>
       </c>
@@ -1765,7 +1777,9 @@
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>168406000000</v>
+      </c>
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="n">
@@ -1802,12 +1816,16 @@
       <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
+      <c r="BQ6" t="n">
+        <v>58558000000</v>
+      </c>
       <c r="BR6" t="inlineStr"/>
       <c r="BS6" t="n">
         <v>5400000000</v>
       </c>
-      <c r="BT6" t="inlineStr"/>
+      <c r="BT6" t="n">
+        <v>10776000000</v>
+      </c>
       <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="inlineStr"/>
       <c r="BW6" t="inlineStr"/>
@@ -1815,7 +1833,9 @@
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="inlineStr"/>
       <c r="CA6" t="inlineStr"/>
-      <c r="CB6" t="inlineStr"/>
+      <c r="CB6" t="n">
+        <v>4827000000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
